--- a/artfynd/A 3575-2026 artfynd.xlsx
+++ b/artfynd/A 3575-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105162288</v>
+        <v>105162289</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603409.2288658437</v>
+        <v>603401</v>
       </c>
       <c r="R2" t="n">
-        <v>7032549.614986388</v>
+        <v>7032605</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105162261</v>
+        <v>105162254</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603411.3896118787</v>
+        <v>603256</v>
       </c>
       <c r="R3" t="n">
-        <v>7032371.677350124</v>
+        <v>7032482</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105162289</v>
+        <v>105162261</v>
       </c>
       <c r="B4" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603401.6172632918</v>
+        <v>603411</v>
       </c>
       <c r="R4" t="n">
-        <v>7032604.517840051</v>
+        <v>7032371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +981,7 @@
         <v>105162286</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,12 +998,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603511.0011907442</v>
+        <v>603511</v>
       </c>
       <c r="R5" t="n">
-        <v>7032470.854229268</v>
+        <v>7032471</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105162290</v>
+        <v>105162253</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603373.9109280444</v>
+        <v>603256</v>
       </c>
       <c r="R6" t="n">
-        <v>7032642.181090987</v>
+        <v>7032482</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,24 +1147,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,12 +1183,7 @@
         <v>105162262</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603410.5939154784</v>
+        <v>603410</v>
       </c>
       <c r="R7" t="n">
-        <v>7032368.512866772</v>
+        <v>7032369</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,19 +1248,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,6 +1274,925 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>105162288</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603409</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7032550</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105162282</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603593</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7032464</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105162290</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603374</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7032642</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105162255</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>603214</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7032479</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105162285</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>603566</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7032469</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105162283</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>603566</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7032469</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105162256</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>603214</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7032480</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105162284</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>603566</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7032469</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105162287</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>603462</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7032485</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 3575-2026 artfynd.xlsx
+++ b/artfynd/A 3575-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162254</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162261</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162286</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162253</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162262</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162288</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162282</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162290</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162255</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162285</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162283</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162256</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162284</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,8 +2272,30 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162287</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>